--- a/forms/trg/Formulir_TRG_nutriepi.xlsx
+++ b/forms/trg/Formulir_TRG_nutriepi.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B21)</f>
+        <f>COUNTA(Anggota!B5:B22)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F21)</f>
+        <f>COUNTA(Anggota!F5:F22)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,18 +913,14 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Rahayu Indriasari, SKM., MPHCN., Ph.D</t>
+          <t>Prof. Dr. drg. A. Zulkifli Abdullah M.Kes</t>
         </is>
       </c>
       <c r="C5" s="12" t="n"/>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Community Nutrition Scientist ( Adolescent Nutrition Specialist)</t>
+          <t>Epidemiogy</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -946,10 +942,14 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dian Sidik Arsyad, SKM., MKM., Ph.D</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="n"/>
+          <t>Rahayu Indriasari, SKM., MPHCN., Ph.D</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Universitas Hasanuddin</t>
@@ -957,18 +957,14 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Non-Communicable Disease Epidemiologist and Public Health Data Scientist</t>
+          <t>Community Nutrition Scientist ( Adolescent Nutrition Specialist)</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-5811-2011</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
@@ -983,21 +979,33 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Malina Osman, MD, MComm. Health</t>
+          <t>Dian Sidik Arsyad, SKM., MKM., Ph.D</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="11" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Non-Communicable Disease Epidemiologist and Public Health Data Scientist</t>
+        </is>
+      </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-5811-2011</t>
+        </is>
+      </c>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
@@ -1012,19 +1020,15 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Wahyuni</t>
+          <t>Prof. Malina Osman, MD, MComm. Health</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
@@ -1045,12 +1049,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>A. Rizky Amaliah</t>
+          <t>Wahyuni</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1058,11 +1062,7 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Reproductive Health</t>
-        </is>
-      </c>
+      <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1080,10 +1080,26 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="11" t="n"/>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>A. Rizky Amaliah</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Reproductive Health</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1091,7 +1107,11 @@
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1280,15 +1300,32 @@
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="12" t="n"/>
     </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_nutriepi.xlsx
+++ b/forms/trg/Formulir_TRG_nutriepi.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. drg. A. Zulkifli Abdullah M.Kes</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
